--- a/Data/EXCEL/Transfer/salemon/202602/9917-salemon-202602.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202602/9917-salemon-202602.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63A494EF-B9DC-4CA3-AF5D-E2C79735BBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E8A0DD8-A08F-4943-AEE2-F06A4C142274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{B47413BC-2A49-42FA-BF94-CBB4498DB182}"/>
+    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{33AD4A17-ADD5-4E2A-A768-3AE0772D4A65}"/>
   </bookViews>
   <sheets>
     <sheet name="9917-salemon-202602" sheetId="2" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E906CB-8BF4-47D1-B557-C8DB95A67442}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749DB22D-E23C-4E4E-AB8B-9BEDD40BF043}">
   <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
